--- a/isolated_excel/MPPM Recalculation.xlsx
+++ b/isolated_excel/MPPM Recalculation.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPPM Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Inputs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MPPM Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Monthly Inputs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Source and Method" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MPPM Summary'!$A$1:$I$4</definedName>
@@ -576,7 +576,7 @@
         <v>21.19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27.82294822884488</v>
+        <v>27.82295583188716</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>114</v>
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.01997540833046796</v>
+        <v>0.01997541333835227</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>26.78749234118261</v>
+        <v>26.78749981121109</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5.597492341182605</v>
+        <v>5.59749981121109</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3</v>
@@ -619,7 +619,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -679,10 +679,10 @@
         <v>0.9631201026442409</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.0228589232346097</v>
+        <v>0.02285947846851455</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9558032954336007</v>
+        <v>0.9558022577656451</v>
       </c>
     </row>
     <row r="3">
@@ -704,10 +704,10 @@
         <v>0.9250752875147531</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-0.06935257224980906</v>
+        <v>-0.06935318755056563</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.154594906718478</v>
+        <v>1.154596433448801</v>
       </c>
     </row>
     <row r="4">
@@ -729,10 +729,10 @@
         <v>0.9976745395509637</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.07341342750790347</v>
+        <v>0.07341404190198397</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.8678925346341463</v>
+        <v>0.8678915411165243</v>
       </c>
     </row>
     <row r="5">
@@ -754,10 +754,10 @@
         <v>0.9797710949826629</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-0.04250438224323216</v>
+        <v>-0.04250464885709748</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.090752984693885</v>
+        <v>1.090753592132677</v>
       </c>
     </row>
     <row r="6">
@@ -779,10 +779,10 @@
         <v>0.9724380915636373</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.3854459628071725</v>
+        <v>0.3854465342164011</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.5209797189043184</v>
+        <v>0.5209792891619205</v>
       </c>
     </row>
     <row r="7">
@@ -804,10 +804,10 @@
         <v>0.9876324120800218</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.001455039942417358</v>
+        <v>0.00145477177200104</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9970962592391395</v>
+        <v>0.9970967932457913</v>
       </c>
     </row>
     <row r="8">
@@ -829,10 +829,10 @@
         <v>0.9601089735562846</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.1241699394124758</v>
+        <v>0.1241699560255558</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.7912907046411373</v>
+        <v>0.7912906812536137</v>
       </c>
     </row>
     <row r="9">
@@ -854,10 +854,10 @@
         <v>0.9939038411792369</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.04356127123718334</v>
+        <v>0.04356127642162821</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9182566743870879</v>
+        <v>0.9182566652632325</v>
       </c>
     </row>
     <row r="10">
@@ -879,10 +879,10 @@
         <v>0.9599867759537827</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.05506381041381037</v>
+        <v>0.055063816693671</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8983437419329015</v>
+        <v>0.8983437312388119</v>
       </c>
     </row>
     <row r="11">
@@ -904,10 +904,10 @@
         <v>0.9549146468467293</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1568497270875411</v>
+        <v>0.1568498521370461</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.7472158972558933</v>
+        <v>0.7472157357155295</v>
       </c>
     </row>
     <row r="12">
@@ -954,10 +954,10 @@
         <v>0.9781287914115532</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0.03592274259403894</v>
+        <v>-0.03592303122981355</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1.075910941391991</v>
+        <v>1.075911585627762</v>
       </c>
     </row>
     <row r="14">
@@ -979,10 +979,10 @@
         <v>0.8946259836989391</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.2702840449401422</v>
+        <v>0.2702846248453648</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.6197239972452336</v>
+        <v>0.6197234314175546</v>
       </c>
     </row>
     <row r="15">
@@ -1004,10 +1004,10 @@
         <v>1.077996580636878</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-0.01484763713349335</v>
+        <v>-0.01484794905117526</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1.030369971438981</v>
+        <v>1.030370623908138</v>
       </c>
     </row>
     <row r="16">
@@ -1029,10 +1029,10 @@
         <v>1.05283346576593</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.04301657591357244</v>
+        <v>-0.04301642328097344</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.091920875938846</v>
+        <v>1.091920527630449</v>
       </c>
     </row>
     <row r="17">
@@ -1054,10 +1054,10 @@
         <v>0.9923697257955202</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.02888747818176995</v>
+        <v>-0.02888722818772815</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1.060378447122946</v>
+        <v>1.060377901175519</v>
       </c>
     </row>
     <row r="18">
@@ -1079,10 +1079,10 @@
         <v>0.9535211430164198</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.1220364164704759</v>
+        <v>0.1220362134342508</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.7943028028520301</v>
+        <v>0.7943030903155814</v>
       </c>
     </row>
     <row r="19">
@@ -1104,10 +1104,10 @@
         <v>0.9878038066806144</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-0.06062881836247813</v>
+        <v>-0.06062881372575712</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1.13324949650653</v>
+        <v>1.133249485319128</v>
       </c>
     </row>
     <row r="20">
@@ -1129,10 +1129,10 @@
         <v>0.9295283057246148</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.03360084344043912</v>
+        <v>0.03360043363907228</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.936039745620866</v>
+        <v>0.9360404878621242</v>
       </c>
     </row>
     <row r="21">
@@ -1154,10 +1154,10 @@
         <v>0.9378842120205459</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.1469148915640635</v>
+        <v>0.1469149378519929</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.7602170693004512</v>
+        <v>0.7602170079377952</v>
       </c>
     </row>
     <row r="22">
@@ -1179,10 +1179,10 @@
         <v>0.9887123252954994</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.001210910917214925</v>
+        <v>0.001211117280586649</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.997582569989793</v>
+        <v>0.9975821587588788</v>
       </c>
     </row>
     <row r="23">
@@ -1204,10 +1204,10 @@
         <v>1.152111238395737</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-0.2497684443831978</v>
+        <v>-0.2497687358911059</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.77668054080037</v>
+        <v>1.776681921485375</v>
       </c>
     </row>
     <row r="24">
@@ -1229,10 +1229,10 @@
         <v>0.9604566236375061</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-0.2240501864079119</v>
+        <v>-0.2240498316814782</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1.660858883384753</v>
+        <v>1.660857364858337</v>
       </c>
     </row>
     <row r="25">
@@ -1254,10 +1254,10 @@
         <v>1.208353246583336</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-0.1831367162106703</v>
+        <v>-0.1831365983806144</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1.498653554788718</v>
+        <v>1.498653122436334</v>
       </c>
     </row>
     <row r="26">
@@ -1279,10 +1279,10 @@
         <v>0.857124786546162</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.07677920166368679</v>
+        <v>0.07677904634156918</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.8624753333095188</v>
+        <v>0.8624755821284482</v>
       </c>
     </row>
     <row r="27">
@@ -1329,10 +1329,10 @@
         <v>0.9622415103954454</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.1640091618973911</v>
+        <v>0.1640090371914322</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.7380524099961332</v>
+        <v>0.7380525681384422</v>
       </c>
     </row>
     <row r="29">
@@ -1354,10 +1354,10 @@
         <v>0.9236868300043514</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.008019258562485865</v>
+        <v>0.008019366556499818</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.9841523660532738</v>
+        <v>0.9841521551792327</v>
       </c>
     </row>
     <row r="30">
@@ -1379,10 +1379,10 @@
         <v>1.140325898830826</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-0.2507480697494133</v>
+        <v>-0.2507480166081368</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1.7813294954971</v>
+        <v>1.781329242812765</v>
       </c>
     </row>
     <row r="31">
@@ -1404,10 +1404,10 @@
         <v>0.8726609769291781</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.2123875276734657</v>
+        <v>0.2123874416839424</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.6803260178502665</v>
+        <v>0.6803261143555749</v>
       </c>
     </row>
     <row r="32">
@@ -1429,10 +1429,10 @@
         <v>0.971861873206222</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.02734005118829974</v>
+        <v>0.02733970018281529</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.9474832932309316</v>
+        <v>0.9474839406738156</v>
       </c>
     </row>
     <row r="33">
@@ -1454,10 +1454,10 @@
         <v>1.032451781203036</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-0.006189136052685562</v>
+        <v>-0.006188796502813454</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1.012494144021466</v>
+        <v>1.01249345215525</v>
       </c>
     </row>
     <row r="34">
@@ -1479,10 +1479,10 @@
         <v>0.9636033160989426</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.03916193560933667</v>
+        <v>0.03916182101195664</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.9260480884582656</v>
+        <v>0.9260482927049738</v>
       </c>
     </row>
     <row r="35">
@@ -1504,10 +1504,10 @@
         <v>0.9580497393985004</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.1548222980792326</v>
+        <v>0.1548229768248279</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.7498418545243757</v>
+        <v>0.7498409730876247</v>
       </c>
     </row>
     <row r="36">
@@ -1529,10 +1529,10 @@
         <v>0.9311717640044544</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.0789969725522417</v>
+        <v>0.07899655285755292</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.8589335125667822</v>
+        <v>0.8589341807615088</v>
       </c>
     </row>
     <row r="37">
@@ -1554,10 +1554,10 @@
         <v>0.9422614020637016</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.08563273435357965</v>
+        <v>0.08563263827225942</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.8484654070775908</v>
+        <v>0.8484655572604007</v>
       </c>
     </row>
     <row r="38">
@@ -1579,10 +1579,10 @@
         <v>1.000784713254058</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.00480219782459379</v>
+        <v>0.004802116302910164</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.9904643473305539</v>
+        <v>0.9904645080474217</v>
       </c>
     </row>
     <row r="39">
@@ -1604,10 +1604,10 @@
         <v>1.187452557550319</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.1429663929865543</v>
+        <v>0.142966566849871</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.765478642883519</v>
+        <v>0.7654784100006868</v>
       </c>
     </row>
     <row r="40">
@@ -1629,10 +1629,10 @@
         <v>1.301695888634536</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>-0.02395659881516721</v>
+        <v>-0.02395688104972504</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1.04969164568266</v>
+        <v>1.049692252744571</v>
       </c>
     </row>
     <row r="41">
@@ -1654,10 +1654,10 @@
         <v>0.7856559601127485</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.1088010733200719</v>
+        <v>0.1088013152362772</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.8133785676803492</v>
+        <v>0.8133782127575467</v>
       </c>
     </row>
     <row r="42">
@@ -1679,10 +1679,10 @@
         <v>0.9111424311350199</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.2146574585577379</v>
+        <v>0.2146573273781289</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.6777856307570337</v>
+        <v>0.677785777154963</v>
       </c>
     </row>
     <row r="43">
@@ -1704,10 +1704,10 @@
         <v>0.9613795399637081</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.07059690810485542</v>
+        <v>0.07059713172355564</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.872465033486761</v>
+        <v>0.8724646690182404</v>
       </c>
     </row>
     <row r="44">
@@ -1729,10 +1729,10 @@
         <v>0.8960977549701413</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.1176064296551937</v>
+        <v>0.1176065186672466</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.8006122239361653</v>
+        <v>0.8006120964062456</v>
       </c>
     </row>
     <row r="45">
@@ -1754,10 +1754,10 @@
         <v>0.870377843369757</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.2599924217301743</v>
+        <v>0.2599921040147133</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.6298891591762703</v>
+        <v>0.6298894768378639</v>
       </c>
     </row>
     <row r="46">
@@ -1779,10 +1779,10 @@
         <v>1.080556042343192</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.01196674898567385</v>
+        <v>0.01196667820718389</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.97648935765467</v>
+        <v>0.9764894942489791</v>
       </c>
     </row>
     <row r="47">
@@ -1804,10 +1804,10 @@
         <v>1.055384676976521</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>-0.07364841160242508</v>
+        <v>-0.07364842202936572</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>1.165328314815024</v>
+        <v>1.165328341048712</v>
       </c>
     </row>
     <row r="48">
@@ -1829,10 +1829,10 @@
         <v>0.8124073373168651</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.06921164451158912</v>
+        <v>0.0692118079226125</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.8747272179228452</v>
+        <v>0.8747269505482094</v>
       </c>
     </row>
     <row r="49">
@@ -1879,10 +1879,10 @@
         <v>1.020502470298805</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>-0.004998333962024648</v>
+        <v>-0.004998113926192538</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>1.010072120591258</v>
+        <v>1.010071673854346</v>
       </c>
     </row>
     <row r="51">
@@ -1904,10 +1904,10 @@
         <v>0.947050922347443</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.05579435935218902</v>
+        <v>0.05579375730410696</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.8971009677018148</v>
+        <v>0.8971019908146478</v>
       </c>
     </row>
     <row r="52">
@@ -1929,10 +1929,10 @@
         <v>0.9178444163991597</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>-0.02636958811626222</v>
+        <v>-0.02636910859368102</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>1.054901083205164</v>
+        <v>1.054900044107555</v>
       </c>
     </row>
     <row r="53">
@@ -1954,10 +1954,10 @@
         <v>0.9012367883774663</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.1244545439682092</v>
+        <v>0.1244545261191403</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.790890196785197</v>
+        <v>0.7908902218936444</v>
       </c>
     </row>
     <row r="54">
@@ -1979,10 +1979,10 @@
         <v>0.9861767286709302</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.08228116793085949</v>
+        <v>0.08228115743632047</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.8537285334541932</v>
+        <v>0.8537285500108659</v>
       </c>
     </row>
     <row r="55">
@@ -2004,10 +2004,10 @@
         <v>0.9548946305726876</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.2316221070924096</v>
+        <v>0.2316218440998432</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.6592422737287004</v>
+        <v>0.659242555269397</v>
       </c>
     </row>
     <row r="56">
@@ -2029,10 +2029,10 @@
         <v>0.9541320909722018</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>-0.02517184608209688</v>
+        <v>-0.02517175280532691</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>1.052310425246981</v>
+        <v>1.052310223865634</v>
       </c>
     </row>
     <row r="57">
@@ -2054,10 +2054,10 @@
         <v>0.9418538915966996</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.1482098338089488</v>
+        <v>0.148210128277273</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.7585033022711357</v>
+        <v>0.7585029132218456</v>
       </c>
     </row>
     <row r="58">
@@ -2079,10 +2079,10 @@
         <v>1.099935334897597</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>-0.07455885054556877</v>
+        <v>-0.07455883142431274</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>1.167622317325235</v>
+        <v>1.167622269074939</v>
       </c>
     </row>
     <row r="59">
@@ -2104,10 +2104,10 @@
         <v>0.8733386651821466</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.2341671178340934</v>
+        <v>0.2341664987009522</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.6565261929864878</v>
+        <v>0.6565268516937636</v>
       </c>
     </row>
     <row r="60">
@@ -2129,10 +2129,10 @@
         <v>1.01400288589504</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.2780535757950808</v>
+        <v>0.2780537130761895</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.6122120599278356</v>
+        <v>0.6122119284073134</v>
       </c>
     </row>
     <row r="61">
@@ -2154,10 +2154,10 @@
         <v>0.9160517804201327</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>-0.09981012664158295</v>
+        <v>-0.09980996264257924</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1.234047151470981</v>
+        <v>1.234046701827069</v>
       </c>
     </row>
     <row r="62">
@@ -2179,10 +2179,10 @@
         <v>1.112119386768055</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>-0.1674542938045153</v>
+        <v>-0.1674544130233561</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>1.442725903371192</v>
+        <v>1.442726316562073</v>
       </c>
     </row>
     <row r="63">
@@ -2204,10 +2204,10 @@
         <v>1.062685451631391</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>-0.004124936148585889</v>
+        <v>-0.00412493647091472</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>1.008301199791404</v>
+        <v>1.008301200444106</v>
       </c>
     </row>
     <row r="64">
@@ -2229,10 +2229,10 @@
         <v>0.9296802682757126</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.1191572741843718</v>
+        <v>0.1191572835340735</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.7983949041001277</v>
+        <v>0.7983948907601723</v>
       </c>
     </row>
     <row r="65">
@@ -2254,10 +2254,10 @@
         <v>1.200190656587331</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>-0.3202741816102964</v>
+        <v>-0.3202741339540492</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>2.164374793455651</v>
+        <v>2.164374489962782</v>
       </c>
     </row>
     <row r="66">
@@ -2279,10 +2279,10 @@
         <v>0.9963421662408478</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.006739867300643132</v>
+        <v>0.006739764154670258</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.986655328411372</v>
+        <v>0.9866555305878084</v>
       </c>
     </row>
     <row r="67">
@@ -2304,10 +2304,10 @@
         <v>1.18803474289766</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>-0.1879710965016489</v>
+        <v>-0.1879711157603117</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>1.516551015734257</v>
+        <v>1.516551087669493</v>
       </c>
     </row>
     <row r="68">
@@ -2329,10 +2329,10 @@
         <v>0.8382858229126688</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.1981662391323191</v>
+        <v>0.1981661379632127</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.696571727774414</v>
+        <v>0.6965718454067523</v>
       </c>
     </row>
     <row r="69">
@@ -2354,10 +2354,10 @@
         <v>1.086837917632202</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>-0.168970147366111</v>
+        <v>-0.1689698670395005</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>1.447993959081158</v>
+        <v>1.447992982194391</v>
       </c>
     </row>
     <row r="70">
@@ -2379,10 +2379,10 @@
         <v>1.213175071407492</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>-0.195534215535247</v>
+        <v>-0.1955341907580299</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>1.545200518371102</v>
+        <v>1.545200423188019</v>
       </c>
     </row>
     <row r="71">
@@ -2404,10 +2404,10 @@
         <v>0.855814644350068</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.1118708590260178</v>
+        <v>0.1118707626471229</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.8088934226411512</v>
+        <v>0.8088935628737396</v>
       </c>
     </row>
     <row r="72">
@@ -2429,10 +2429,10 @@
         <v>0.8969474204044003</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.2541550854108761</v>
+        <v>0.2541549965748526</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.6357663138080891</v>
+        <v>0.6357664038750319</v>
       </c>
     </row>
     <row r="73">
@@ -2479,10 +2479,10 @@
         <v>0.8852560567072887</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.3368690408023851</v>
+        <v>0.3368689099972106</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.5595285714048601</v>
+        <v>0.559528680898372</v>
       </c>
     </row>
     <row r="75">
@@ -2504,10 +2504,10 @@
         <v>1.050645569002066</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.1883090204628883</v>
+        <v>0.1883093324211624</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.7081760126833728</v>
+        <v>0.708175640858745</v>
       </c>
     </row>
     <row r="76">
@@ -2529,10 +2529,10 @@
         <v>0.9304259309730823</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.1966627426546637</v>
+        <v>0.1966626279293711</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.6983231837451835</v>
+        <v>0.698323317643132</v>
       </c>
     </row>
     <row r="77">
@@ -2554,10 +2554,10 @@
         <v>0.9694982234937056</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>-0.001007890208774564</v>
+        <v>-0.001008096561490035</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>1.002018832046165</v>
+        <v>1.00201924600213</v>
       </c>
     </row>
     <row r="78">
@@ -2579,10 +2579,10 @@
         <v>0.9913625810824932</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.3634361137902264</v>
+        <v>0.3634364393620109</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.5379357577879215</v>
+        <v>0.5379355008831204</v>
       </c>
     </row>
     <row r="79">
@@ -2604,10 +2604,10 @@
         <v>0.8798812409728222</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.1182107222049846</v>
+        <v>0.1182105081934617</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.7997471396255472</v>
+        <v>0.7997474457488012</v>
       </c>
     </row>
     <row r="80">
@@ -2629,10 +2629,10 @@
         <v>0.9387194711195235</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.1046522501830784</v>
+        <v>0.1046521692853788</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.8194997716485158</v>
+        <v>0.8194998916784232</v>
       </c>
     </row>
     <row r="81">
@@ -2654,10 +2654,10 @@
         <v>1.032619118725376</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.05619638947121319</v>
+        <v>0.05619656225124547</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.8964181534612434</v>
+        <v>0.8964178601765456</v>
       </c>
     </row>
     <row r="82">
@@ -2679,10 +2679,10 @@
         <v>1.10263682294205</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>-0.1185779838893664</v>
+        <v>-0.1185780613309324</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>1.287159041868577</v>
+        <v>1.287159268047691</v>
       </c>
     </row>
     <row r="83">
@@ -2704,10 +2704,10 @@
         <v>1.043418468810109</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>-0.06250733080244375</v>
+        <v>-0.06250724843451383</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>1.137795571744597</v>
+        <v>1.137795371811613</v>
       </c>
     </row>
     <row r="84">
@@ -2729,10 +2729,10 @@
         <v>0.8396361081156987</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.1468859664536928</v>
+        <v>0.1468858727358351</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.760255415989783</v>
+        <v>0.7602555402384349</v>
       </c>
     </row>
     <row r="85">
@@ -2754,10 +2754,10 @@
         <v>0.9149756157506371</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.05893396491449421</v>
+        <v>0.05893429659056126</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.8917892713472102</v>
+        <v>0.8917887127004409</v>
       </c>
     </row>
     <row r="86">
@@ -2779,10 +2779,10 @@
         <v>0.9672203593217011</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.2424177159424299</v>
+        <v>0.2424174283204805</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.6478354795787929</v>
+        <v>0.6478357795290686</v>
       </c>
     </row>
     <row r="87">
@@ -2829,10 +2829,10 @@
         <v>0.9386281887403397</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.1421811675620739</v>
+        <v>0.1421810709527707</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.7665315054625226</v>
+        <v>0.7665316351338675</v>
       </c>
     </row>
     <row r="89">
@@ -2854,10 +2854,10 @@
         <v>1.086982276900574</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>-0.04376020231617472</v>
+        <v>-0.04376012143437502</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>1.093619815715721</v>
+        <v>1.093619630712068</v>
       </c>
     </row>
     <row r="90">
@@ -2904,10 +2904,10 @@
         <v>0.9319221176611617</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.1269430297426406</v>
+        <v>0.1269428903211811</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.7874012075855628</v>
+        <v>0.7874014024146588</v>
       </c>
     </row>
     <row r="92">
@@ -2929,10 +2929,10 @@
         <v>0.9760924573374677</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>-0.05277653562964368</v>
+        <v>-0.05277641844244729</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>1.114538575489416</v>
+        <v>1.114538299715786</v>
       </c>
     </row>
     <row r="93">
@@ -2954,10 +2954,10 @@
         <v>0.9531969858300583</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.02008214562373478</v>
+        <v>0.02008208031891745</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.9610139846261756</v>
+        <v>0.9610141076728321</v>
       </c>
     </row>
     <row r="94">
@@ -2979,10 +2979,10 @@
         <v>0.9586163156807694</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.0174280680549439</v>
+        <v>0.01742800515149523</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.9660343541510192</v>
+        <v>0.9660344736029981</v>
       </c>
     </row>
     <row r="95">
@@ -3004,10 +3004,10 @@
         <v>1.018385718385046</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.09321448185288306</v>
+        <v>0.09321487111885762</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.8367375279135763</v>
+        <v>0.8367369320318335</v>
       </c>
     </row>
     <row r="96">
@@ -3029,10 +3029,10 @@
         <v>0.8921825152855977</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.04135301734180707</v>
+        <v>0.04135277759167555</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.922155244464525</v>
+        <v>0.9221556690792596</v>
       </c>
     </row>
     <row r="97">
@@ -3079,10 +3079,10 @@
         <v>0.9465483128657197</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>-0.1058902751059577</v>
+        <v>-0.1058902182082808</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>1.250887817393697</v>
+        <v>1.250887658190409</v>
       </c>
     </row>
     <row r="99">
@@ -3104,10 +3104,10 @@
         <v>1.026615030088406</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.04039309306242167</v>
+        <v>0.04039309049196182</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.9238576924744808</v>
+        <v>0.9238576970395613</v>
       </c>
     </row>
     <row r="100">
@@ -3129,10 +3129,10 @@
         <v>1.122982133980397</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>-0.1323249309931265</v>
+        <v>-0.1323249840648691</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>1.328268159144804</v>
+        <v>1.328268321633079</v>
       </c>
     </row>
     <row r="101">
@@ -3254,10 +3254,10 @@
         <v>0.9606567708776664</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>-0.02074555918313137</v>
+        <v>-0.02074547328268472</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>1.042818916545825</v>
+        <v>1.042818733593172</v>
       </c>
     </row>
     <row r="106">
@@ -3279,10 +3279,10 @@
         <v>0.930810829949856</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.07125121360969189</v>
+        <v>0.07125111963927333</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.8713995796872697</v>
+        <v>0.8713997325660584</v>
       </c>
     </row>
     <row r="107">
@@ -3354,10 +3354,10 @@
         <v>0.9987769482420827</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>0.05373101785259271</v>
+        <v>0.05373093153479269</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>0.9006176866714778</v>
+        <v>0.9006178342221252</v>
       </c>
     </row>
     <row r="110">
@@ -3379,10 +3379,10 @@
         <v>0.9716183111985258</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0.02482573320254033</v>
+        <v>0.02482581715253174</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0.9521381268406037</v>
+        <v>0.952137970849248</v>
       </c>
     </row>
     <row r="111">

--- a/isolated_excel/MPPM Recalculation.xlsx
+++ b/isolated_excel/MPPM Recalculation.xlsx
@@ -576,7 +576,7 @@
         <v>21.19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27.82295583188716</v>
+        <v>27.82296257687193</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>114</v>
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.01997541333835227</v>
+        <v>0.01997541778106075</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>26.78749981121109</v>
+        <v>26.78750643819328</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5.59749981121109</v>
+        <v>5.597506438193275</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3</v>
@@ -619,7 +619,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -679,10 +679,10 @@
         <v>0.9631201026442409</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.02285947846851455</v>
+        <v>0.02285938765936324</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9558022577656451</v>
+        <v>0.9558024274773312</v>
       </c>
     </row>
     <row r="3">
@@ -704,10 +704,10 @@
         <v>0.9250752875147531</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-0.06935318755056563</v>
+        <v>-0.06935301614831746</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.154596433448801</v>
+        <v>1.1545960081524</v>
       </c>
     </row>
     <row r="4">
@@ -729,10 +729,10 @@
         <v>0.9976745395509637</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.07341404190198397</v>
+        <v>0.07341384410724183</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.8678915411165243</v>
+        <v>0.8678918609640842</v>
       </c>
     </row>
     <row r="5">
@@ -754,10 +754,10 @@
         <v>0.9797710949826629</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-0.04250464885709748</v>
+        <v>-0.04250420827805912</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.090753592132677</v>
+        <v>1.090752588341199</v>
       </c>
     </row>
     <row r="6">
@@ -779,10 +779,10 @@
         <v>0.9724380915636373</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.3854465342164011</v>
+        <v>0.3854460198478553</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.5209792891619205</v>
+        <v>0.5209796760054427</v>
       </c>
     </row>
     <row r="7">
@@ -829,10 +829,10 @@
         <v>0.9601089735562846</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.1241699560255558</v>
+        <v>0.1241695546462829</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.7912906812536137</v>
+        <v>0.7912912463066943</v>
       </c>
     </row>
     <row r="9">
@@ -854,10 +854,10 @@
         <v>0.9939038411792369</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.04356127642162821</v>
+        <v>0.04356176803515321</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9182566652632325</v>
+        <v>0.9182558000968312</v>
       </c>
     </row>
     <row r="10">
@@ -879,10 +879,10 @@
         <v>0.9599867759537827</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.055063816693671</v>
+        <v>0.05506381041381037</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8983437312388119</v>
+        <v>0.8983437419329015</v>
       </c>
     </row>
     <row r="11">
@@ -904,10 +904,10 @@
         <v>0.9549146468467293</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1568498521370461</v>
+        <v>0.1568498351823857</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.7472157357155295</v>
+        <v>0.7472157576177483</v>
       </c>
     </row>
     <row r="12">
@@ -929,10 +929,10 @@
         <v>0.9413715807084023</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-0.02882134310480688</v>
+        <v>-0.02882199448448508</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1.060234033277098</v>
+        <v>1.06023545549863</v>
       </c>
     </row>
     <row r="13">
@@ -954,10 +954,10 @@
         <v>0.9781287914115532</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0.03592303122981355</v>
+        <v>-0.03592218605934583</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1.075911585627762</v>
+        <v>1.075909699206798</v>
       </c>
     </row>
     <row r="14">
@@ -979,10 +979,10 @@
         <v>0.8946259836989391</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.2702846248453648</v>
+        <v>0.2702840449401422</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.6197234314175546</v>
+        <v>0.6197239972452336</v>
       </c>
     </row>
     <row r="15">
@@ -1004,10 +1004,10 @@
         <v>1.077996580636878</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-0.01484794905117526</v>
+        <v>-0.01484763713349335</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1.030370623908138</v>
+        <v>1.030369971438981</v>
       </c>
     </row>
     <row r="16">
@@ -1029,10 +1029,10 @@
         <v>1.05283346576593</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.04301642328097344</v>
+        <v>-0.04301649616685432</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.091920527630449</v>
+        <v>1.091920693956393</v>
       </c>
     </row>
     <row r="17">
@@ -1054,10 +1054,10 @@
         <v>0.9923697257955202</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.02888722818772815</v>
+        <v>-0.02888722578051672</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1.060377901175519</v>
+        <v>1.060377895918552</v>
       </c>
     </row>
     <row r="18">
@@ -1079,10 +1079,10 @@
         <v>0.9535211430164198</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.1220362134342508</v>
+        <v>0.1220363745826194</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.7943030903155814</v>
+        <v>0.7943028621578481</v>
       </c>
     </row>
     <row r="19">
@@ -1104,10 +1104,10 @@
         <v>0.9878038066806144</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-0.06062881372575712</v>
+        <v>-0.06062918220140889</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1.133249485319128</v>
+        <v>1.133250374371495</v>
       </c>
     </row>
     <row r="20">
@@ -1129,10 +1129,10 @@
         <v>0.9295283057246148</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.03360043363907228</v>
+        <v>0.03360076476281404</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.9360404878621242</v>
+        <v>0.9360398881234443</v>
       </c>
     </row>
     <row r="21">
@@ -1154,10 +1154,10 @@
         <v>0.9378842120205459</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.1469149378519929</v>
+        <v>0.146914757174905</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.7602170079377952</v>
+        <v>0.7602172474565654</v>
       </c>
     </row>
     <row r="22">
@@ -1179,10 +1179,10 @@
         <v>0.9887123252954994</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.001211117280586649</v>
+        <v>0.001211391988220623</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.9975821587588788</v>
+        <v>0.9975816113352296</v>
       </c>
     </row>
     <row r="23">
@@ -1204,10 +1204,10 @@
         <v>1.152111238395737</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-0.2497687358911059</v>
+        <v>-0.2497689417360024</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.776681921485375</v>
+        <v>1.776682896440897</v>
       </c>
     </row>
     <row r="24">
@@ -1279,10 +1279,10 @@
         <v>0.857124786546162</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.07677904634156918</v>
+        <v>0.0767789742180931</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.8624755821284482</v>
+        <v>0.8624756976669954</v>
       </c>
     </row>
     <row r="27">
@@ -1304,10 +1304,10 @@
         <v>0.9387485503786788</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.07421903283671338</v>
+        <v>0.07421923875024605</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.8665912791983643</v>
+        <v>0.8665909469703643</v>
       </c>
     </row>
     <row r="28">
@@ -1329,10 +1329,10 @@
         <v>0.9622415103954454</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.1640090371914322</v>
+        <v>0.164008517914757</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.7380525681384422</v>
+        <v>0.7380532266449107</v>
       </c>
     </row>
     <row r="29">
@@ -1354,10 +1354,10 @@
         <v>0.9236868300043514</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.008019366556499818</v>
+        <v>0.008019690538680679</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.9841521551792327</v>
+        <v>0.9841515225572447</v>
       </c>
     </row>
     <row r="30">
@@ -1379,10 +1379,10 @@
         <v>1.140325898830826</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-0.2507480166081368</v>
+        <v>-0.2507480697494133</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1.781329242812765</v>
+        <v>1.7813294954971</v>
       </c>
     </row>
     <row r="31">
@@ -1404,10 +1404,10 @@
         <v>0.8726609769291781</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.2123874416839424</v>
+        <v>0.2123879532281372</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.6803261143555749</v>
+        <v>0.6803255402541909</v>
       </c>
     </row>
     <row r="32">
@@ -1429,10 +1429,10 @@
         <v>0.971861873206222</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.02733970018281529</v>
+        <v>0.02733945658285974</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.9474839406738156</v>
+        <v>0.9474843900035317</v>
       </c>
     </row>
     <row r="33">
@@ -1454,10 +1454,10 @@
         <v>1.032451781203036</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-0.006188796502813454</v>
+        <v>-0.006188681909835902</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1.01249345215525</v>
+        <v>1.012493218660963</v>
       </c>
     </row>
     <row r="34">
@@ -1479,10 +1479,10 @@
         <v>0.9636033160989426</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.03916182101195664</v>
+        <v>0.03916169743892106</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.9260482927049738</v>
+        <v>0.9260485129490527</v>
       </c>
     </row>
     <row r="35">
@@ -1504,10 +1504,10 @@
         <v>0.9580497393985004</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.1548229768248279</v>
+        <v>0.1548226289151955</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.7498409730876247</v>
+        <v>0.7498414248919626</v>
       </c>
     </row>
     <row r="36">
@@ -1529,10 +1529,10 @@
         <v>0.9311717640044544</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.07899655285755292</v>
+        <v>0.07899666343896872</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.8589341807615088</v>
+        <v>0.858934004705074</v>
       </c>
     </row>
     <row r="37">
@@ -1554,10 +1554,10 @@
         <v>0.9422614020637016</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.08563263827225942</v>
+        <v>0.08563255734836273</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.8484655572604007</v>
+        <v>0.8484656837509729</v>
       </c>
     </row>
     <row r="38">
@@ -1579,10 +1579,10 @@
         <v>1.000784713254058</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.004802116302910164</v>
+        <v>0.004802606216045779</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.9904645080474217</v>
+        <v>0.9904635422030826</v>
       </c>
     </row>
     <row r="39">
@@ -1604,10 +1604,10 @@
         <v>1.187452557550319</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.142966566849871</v>
+        <v>0.1429661147929286</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.7654784100006868</v>
+        <v>0.7654790155127723</v>
       </c>
     </row>
     <row r="40">
@@ -1629,10 +1629,10 @@
         <v>1.301695888634536</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>-0.02395688104972504</v>
+        <v>-0.02395666979894417</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1.049692252744571</v>
+        <v>1.049691798362522</v>
       </c>
     </row>
     <row r="41">
@@ -1654,10 +1654,10 @@
         <v>0.7856559601127485</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.1088013152362772</v>
+        <v>0.1088012994108971</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.8133782127575467</v>
+        <v>0.8133782359754479</v>
       </c>
     </row>
     <row r="42">
@@ -1679,10 +1679,10 @@
         <v>0.9111424311350199</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.2146573273781289</v>
+        <v>0.2146570368602847</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.677785777154963</v>
+        <v>0.6777861013763365</v>
       </c>
     </row>
     <row r="43">
@@ -1704,10 +1704,10 @@
         <v>0.9613795399637081</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.07059713172355564</v>
+        <v>0.07059713934785017</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.8724646690182404</v>
+        <v>0.8724646565916658</v>
       </c>
     </row>
     <row r="44">
@@ -1729,10 +1729,10 @@
         <v>0.8960977549701413</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.1176065186672466</v>
+        <v>0.1176068331579609</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.8006120964062456</v>
+        <v>0.800611645827335</v>
       </c>
     </row>
     <row r="45">
@@ -1754,10 +1754,10 @@
         <v>0.870377843369757</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.2599921040147133</v>
+        <v>0.2599919668202599</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.6298894768378639</v>
+        <v>0.6298896140091308</v>
       </c>
     </row>
     <row r="46">
@@ -1779,10 +1779,10 @@
         <v>1.080556042343192</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.01196667820718389</v>
+        <v>0.01196646244274691</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.9764894942489791</v>
+        <v>0.9764899106495937</v>
       </c>
     </row>
     <row r="47">
@@ -1804,10 +1804,10 @@
         <v>1.055384676976521</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>-0.07364842202936572</v>
+        <v>-0.07364829087902502</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>1.165328341048712</v>
+        <v>1.165328011080739</v>
       </c>
     </row>
     <row r="48">
@@ -1854,10 +1854,10 @@
         <v>0.9273208253828208</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>-0.02556747199089759</v>
+        <v>-0.0255675434609216</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>1.053165088388704</v>
+        <v>1.053165242878092</v>
       </c>
     </row>
     <row r="50">
@@ -1879,10 +1879,10 @@
         <v>1.020502470298805</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>-0.004998113926192538</v>
+        <v>-0.004998114292780631</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>1.010071673854346</v>
+        <v>1.010071674598626</v>
       </c>
     </row>
     <row r="51">
@@ -1904,10 +1904,10 @@
         <v>0.947050922347443</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.05579375730410696</v>
+        <v>0.05579398255800871</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.8971019908146478</v>
+        <v>0.8971016080208348</v>
       </c>
     </row>
     <row r="52">
@@ -1929,10 +1929,10 @@
         <v>0.9178444163991597</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>-0.02636910859368102</v>
+        <v>-0.02636931436640821</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>1.054900044107555</v>
+        <v>1.054900490004927</v>
       </c>
     </row>
     <row r="53">
@@ -1954,10 +1954,10 @@
         <v>0.9012367883774663</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.1244545261191403</v>
+        <v>0.1244544633344791</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.7908902218936444</v>
+        <v>0.7908903102134078</v>
       </c>
     </row>
     <row r="54">
@@ -1979,10 +1979,10 @@
         <v>0.9861767286709302</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.08228115743632047</v>
+        <v>0.08228116793085949</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.8537285500108659</v>
+        <v>0.8537285334541932</v>
       </c>
     </row>
     <row r="55">
@@ -2004,10 +2004,10 @@
         <v>0.9548946305726876</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.2316218440998432</v>
+        <v>0.2316222249405868</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.659242555269397</v>
+        <v>0.6592421475690794</v>
       </c>
     </row>
     <row r="56">
@@ -2029,10 +2029,10 @@
         <v>0.9541320909722018</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>-0.02517175280532691</v>
+        <v>-0.02517184367352054</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>1.052310223865634</v>
+        <v>1.052310420046947</v>
       </c>
     </row>
     <row r="57">
@@ -2054,10 +2054,10 @@
         <v>0.9418538915966996</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.148210128277273</v>
+        <v>0.1482101137295451</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.7585029132218456</v>
+        <v>0.758502932442185</v>
       </c>
     </row>
     <row r="58">
@@ -2079,10 +2079,10 @@
         <v>1.099935334897597</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>-0.07455883142431274</v>
+        <v>-0.07455908150910806</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>1.167622269074939</v>
+        <v>1.167622900135464</v>
       </c>
     </row>
     <row r="59">
@@ -2104,10 +2104,10 @@
         <v>0.8733386651821466</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.2341664987009522</v>
+        <v>0.2341669114563416</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.6565268516937636</v>
+        <v>0.6565264125555101</v>
       </c>
     </row>
     <row r="60">
@@ -2129,10 +2129,10 @@
         <v>1.01400288589504</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.2780537130761895</v>
+        <v>0.2780535217596904</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.6122119284073134</v>
+        <v>0.6122121116958058</v>
       </c>
     </row>
     <row r="61">
@@ -2154,10 +2154,10 @@
         <v>0.9160517804201327</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>-0.09980996264257924</v>
+        <v>-0.09981002120570948</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1.234046701827069</v>
+        <v>1.234046862392376</v>
       </c>
     </row>
     <row r="62">
@@ -2179,10 +2179,10 @@
         <v>1.112119386768055</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>-0.1674544130233561</v>
+        <v>-0.1674542287481032</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>1.442726316562073</v>
+        <v>1.442725677897541</v>
       </c>
     </row>
     <row r="63">
@@ -2204,10 +2204,10 @@
         <v>1.062685451631391</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>-0.00412493647091472</v>
+        <v>-0.004124935826256948</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>1.008301200444106</v>
+        <v>1.008301199138703</v>
       </c>
     </row>
     <row r="64">
@@ -2229,10 +2229,10 @@
         <v>0.9296802682757126</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.1191572835340735</v>
+        <v>0.1191571079042555</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.7983948907601723</v>
+        <v>0.7983951413451159</v>
       </c>
     </row>
     <row r="65">
@@ -2254,10 +2254,10 @@
         <v>1.200190656587331</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>-0.3202741339540492</v>
+        <v>-0.3202740638430636</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>2.164374489962782</v>
+        <v>2.164374043469827</v>
       </c>
     </row>
     <row r="66">
@@ -2279,10 +2279,10 @@
         <v>0.9963421662408478</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.006739764154670258</v>
+        <v>0.006739763459490788</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.9866555305878084</v>
+        <v>0.98665553195043</v>
       </c>
     </row>
     <row r="67">
@@ -2304,10 +2304,10 @@
         <v>1.18803474289766</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>-0.1879711157603117</v>
+        <v>-0.1879710965016489</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>1.516551087669493</v>
+        <v>1.516551015734257</v>
       </c>
     </row>
     <row r="68">
@@ -2329,10 +2329,10 @@
         <v>0.8382858229126688</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.1981661379632127</v>
+        <v>0.1981657344436987</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.6965718454067523</v>
+        <v>0.6965723145912263</v>
       </c>
     </row>
     <row r="69">
@@ -2354,10 +2354,10 @@
         <v>1.086837917632202</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>-0.1689698670395005</v>
+        <v>-0.1689697446694109</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>1.447992982194391</v>
+        <v>1.447992555757407</v>
       </c>
     </row>
     <row r="70">
@@ -2379,10 +2379,10 @@
         <v>1.213175071407492</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>-0.1955341907580299</v>
+        <v>-0.1955340764311234</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>1.545200423188019</v>
+        <v>1.545199983994844</v>
       </c>
     </row>
     <row r="71">
@@ -2404,10 +2404,10 @@
         <v>0.855814644350068</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.1118707626471229</v>
+        <v>0.1118706750789171</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.8088935628737396</v>
+        <v>0.8088936902866886</v>
       </c>
     </row>
     <row r="72">
@@ -2429,10 +2429,10 @@
         <v>0.8969474204044003</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.2541549965748526</v>
+        <v>0.2541551382415801</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.6357664038750319</v>
+        <v>0.6357662602453675</v>
       </c>
     </row>
     <row r="73">
@@ -2454,10 +2454,10 @@
         <v>1.126011828926274</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>-0.1364415773216663</v>
+        <v>-0.13644167486741</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>1.340962247464996</v>
+        <v>1.340962550409599</v>
       </c>
     </row>
     <row r="74">
@@ -2554,10 +2554,10 @@
         <v>0.9694982234937056</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>-0.001008096561490035</v>
+        <v>-0.001008165368845293</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>1.00201924600213</v>
+        <v>1.002019384033882</v>
       </c>
     </row>
     <row r="78">
@@ -2579,10 +2579,10 @@
         <v>0.9913625810824932</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.3634364393620109</v>
+        <v>0.3634365332711422</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.5379355008831204</v>
+        <v>0.5379354267805821</v>
       </c>
     </row>
     <row r="79">
@@ -2604,10 +2604,10 @@
         <v>0.8798812409728222</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.1182105081934617</v>
+        <v>0.1182106092275659</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.7997474457488012</v>
+        <v>0.7997473012290435</v>
       </c>
     </row>
     <row r="80">
@@ -2629,10 +2629,10 @@
         <v>0.9387194711195235</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.1046521692853788</v>
+        <v>0.1046520694763253</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.8194998916784232</v>
+        <v>0.819500039767608</v>
       </c>
     </row>
     <row r="81">
@@ -2654,10 +2654,10 @@
         <v>1.032619118725376</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.05619656225124547</v>
+        <v>0.05619664404476143</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.8964178601765456</v>
+        <v>0.8964177213365556</v>
       </c>
     </row>
     <row r="82">
@@ -2679,10 +2679,10 @@
         <v>1.10263682294205</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>-0.1185780613309324</v>
+        <v>-0.1185781295896224</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>1.287159268047691</v>
+        <v>1.287159467406958</v>
       </c>
     </row>
     <row r="83">
@@ -2754,10 +2754,10 @@
         <v>0.9149756157506371</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.05893429659056126</v>
+        <v>0.05893413316042428</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.8917887127004409</v>
+        <v>0.8917889879681051</v>
       </c>
     </row>
     <row r="86">
@@ -2779,10 +2779,10 @@
         <v>0.9672203593217011</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.2424174283204805</v>
+        <v>0.242417620068432</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.6478357795290686</v>
+        <v>0.6478355795622104</v>
       </c>
     </row>
     <row r="87">
@@ -2829,10 +2829,10 @@
         <v>0.9386281887403397</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.1421810709527707</v>
+        <v>0.1421811675620739</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.7665316351338675</v>
+        <v>0.7665315054625226</v>
       </c>
     </row>
     <row r="89">
@@ -2854,10 +2854,10 @@
         <v>1.086982276900574</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>-0.04376012143437502</v>
+        <v>-0.0437602868993443</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>1.093619630712068</v>
+        <v>1.093620009185691</v>
       </c>
     </row>
     <row r="90">
@@ -2879,10 +2879,10 @@
         <v>0.9077465777794721</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.2688711155456016</v>
+        <v>0.2688710508743717</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.6211049314641301</v>
+        <v>0.6211049947765067</v>
       </c>
     </row>
     <row r="91">
@@ -2904,10 +2904,10 @@
         <v>0.9319221176611617</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.1269428903211811</v>
+        <v>0.1269431868627044</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.7874014024146588</v>
+        <v>0.7874009880243269</v>
       </c>
     </row>
     <row r="92">
@@ -2929,10 +2929,10 @@
         <v>0.9760924573374677</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>-0.05277641844244729</v>
+        <v>-0.05277653562964368</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>1.114538299715786</v>
+        <v>1.114538575489416</v>
       </c>
     </row>
     <row r="93">
@@ -2954,10 +2954,10 @@
         <v>0.9531969858300583</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.02008208031891745</v>
+        <v>0.02008214562373478</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.9610141076728321</v>
+        <v>0.9610139846261756</v>
       </c>
     </row>
     <row r="94">
@@ -2979,10 +2979,10 @@
         <v>0.9586163156807694</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.01742800515149523</v>
+        <v>0.01742800403576883</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.9660344736029981</v>
+        <v>0.9660344757217331</v>
       </c>
     </row>
     <row r="95">
@@ -3004,10 +3004,10 @@
         <v>1.018385718385046</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.09321487111885762</v>
+        <v>0.09321467648585813</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.8367369320318335</v>
+        <v>0.836737229972644</v>
       </c>
     </row>
     <row r="96">
@@ -3029,10 +3029,10 @@
         <v>0.8921825152855977</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.04135277759167555</v>
+        <v>0.04135289746672743</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.9221556690792596</v>
+        <v>0.9221554567718803</v>
       </c>
     </row>
     <row r="97">
@@ -3054,10 +3054,10 @@
         <v>1.049436799471192</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>-0.02857680729967016</v>
+        <v>-0.02857691784311611</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>1.059700316247135</v>
+        <v>1.059700557425121</v>
       </c>
     </row>
     <row r="98">
@@ -3079,10 +3079,10 @@
         <v>0.9465483128657197</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>-0.1058902182082808</v>
+        <v>-0.1058901733604136</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>1.250887658190409</v>
+        <v>1.25088753270327</v>
       </c>
     </row>
     <row r="99">
@@ -3104,10 +3104,10 @@
         <v>1.026615030088406</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.04039309049196182</v>
+        <v>0.04039309306242167</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.9238576970395613</v>
+        <v>0.9238576924744808</v>
       </c>
     </row>
     <row r="100">
@@ -3129,10 +3129,10 @@
         <v>1.122982133980397</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>-0.1323249840648691</v>
+        <v>-0.1323249309931265</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>1.328268321633079</v>
+        <v>1.328268159144804</v>
       </c>
     </row>
     <row r="101">
@@ -3179,10 +3179,10 @@
         <v>0.8850712241425256</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>0.2406355273027898</v>
+        <v>0.240635387014742</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0.6496980641659276</v>
+        <v>0.6496982110985062</v>
       </c>
     </row>
     <row r="103">
@@ -3204,10 +3204,10 @@
         <v>0.9055585326855982</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0.1692515633256428</v>
+        <v>0.1692516955417807</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.7314490522216738</v>
+        <v>0.7314488868007236</v>
       </c>
     </row>
     <row r="104">

--- a/isolated_excel/MPPM Recalculation.xlsx
+++ b/isolated_excel/MPPM Recalculation.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MPPM Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Monthly Inputs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Source and Method" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPPM Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Inputs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MPPM Summary'!$A$1:$I$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Monthly Inputs'!$A$1:$G$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Monthly Inputs'!$A$1:$G$116</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source and Method'!$A$1:$B$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -510,24 +510,24 @@
         <v>35.16</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>46.57265489959113</v>
+        <v>46.57265489959188</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.03262752823095071</v>
+        <v>0.03263370241484337</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>47.0023852738126</v>
+        <v>47.01293292530049</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>11.8423852738126</v>
+        <v>11.85293292530049</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>3</v>
@@ -546,21 +546,21 @@
         <v>12.80668196833166</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.009916832011085525</v>
+        <v>0.009824109332120121</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>12.57120795593889</v>
+        <v>12.44724565179145</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>4.201207955938891</v>
+        <v>4.077245651791451</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>3</v>
@@ -576,24 +576,24 @@
         <v>21.19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27.82296257687193</v>
+        <v>27.82296044992847</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.01997541778106075</v>
+        <v>0.0198279274293732</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>26.78750643819328</v>
+        <v>26.56767680106729</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5.597506438193275</v>
+        <v>5.377676801067285</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3</v>
@@ -611,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -679,10 +679,10 @@
         <v>0.9631201026442409</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.02285938765936324</v>
+        <v>0.02285892531040834</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9558024274773312</v>
+        <v>0.95580329155417</v>
       </c>
     </row>
     <row r="3">
@@ -704,10 +704,10 @@
         <v>0.9250752875147531</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-0.06935301614831746</v>
+        <v>-0.06935284474603898</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.1545960081524</v>
+        <v>1.15459558285616</v>
       </c>
     </row>
     <row r="4">
@@ -729,10 +729,10 @@
         <v>0.9976745395509637</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.07341384410724183</v>
+        <v>0.07341355091686697</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.8678918609640842</v>
+        <v>0.8678923350732001</v>
       </c>
     </row>
     <row r="5">
@@ -754,10 +754,10 @@
         <v>0.9797710949826629</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-0.04250420827805912</v>
+        <v>-0.04250421583286856</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.090752588341199</v>
+        <v>1.090752605553657</v>
       </c>
     </row>
     <row r="6">
@@ -779,10 +779,10 @@
         <v>0.9724380915636373</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.3854460198478553</v>
+        <v>0.3854462770320806</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.5209796760054427</v>
+        <v>0.5209794825836636</v>
       </c>
     </row>
     <row r="7">
@@ -804,10 +804,10 @@
         <v>0.9876324120800218</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.00145477177200104</v>
+        <v>0.001454972753595296</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9970967932457913</v>
+        <v>0.9970963930319254</v>
       </c>
     </row>
     <row r="8">
@@ -829,10 +829,10 @@
         <v>0.9601089735562846</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.1241695546462829</v>
+        <v>0.1241693290371488</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.7912912463066943</v>
+        <v>0.7912915639146314</v>
       </c>
     </row>
     <row r="9">
@@ -854,10 +854,10 @@
         <v>0.9939038411792369</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.04356176803515321</v>
+        <v>0.04356141099001598</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9182558000968312</v>
+        <v>0.9182564284428408</v>
       </c>
     </row>
     <row r="10">
@@ -879,10 +879,10 @@
         <v>0.9599867759537827</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.05506381041381037</v>
+        <v>0.05506394330039477</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8983437419329015</v>
+        <v>0.8983435156379461</v>
       </c>
     </row>
     <row r="11">
@@ -904,10 +904,10 @@
         <v>0.9549146468467293</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1568498351823857</v>
+        <v>0.1568495448071063</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.7472157576177483</v>
+        <v>0.7472161327279129</v>
       </c>
     </row>
     <row r="12">
@@ -929,10 +929,10 @@
         <v>0.9413715807084023</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-0.02882199448448508</v>
+        <v>-0.02882116699895132</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1.06023545549863</v>
+        <v>1.060233648768297</v>
       </c>
     </row>
     <row r="13">
@@ -954,10 +954,10 @@
         <v>0.9781287914115532</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0.03592218605934583</v>
+        <v>-0.03592226844671587</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1.075909699206798</v>
+        <v>1.075909883095237</v>
       </c>
     </row>
     <row r="14">
@@ -979,10 +979,10 @@
         <v>0.8946259836989391</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.2702840449401422</v>
+        <v>0.270283864222761</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.6197239972452336</v>
+        <v>0.6197241735757516</v>
       </c>
     </row>
     <row r="15">
@@ -1004,10 +1004,10 @@
         <v>1.077996580636878</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-0.01484763713349335</v>
+        <v>-0.01484787048851988</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1.030369971438981</v>
+        <v>1.03037045957078</v>
       </c>
     </row>
     <row r="16">
@@ -1029,10 +1029,10 @@
         <v>1.05283346576593</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.04301649616685432</v>
+        <v>-0.04301649959727905</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.091920693956393</v>
+        <v>1.09192070178464</v>
       </c>
     </row>
     <row r="17">
@@ -1054,10 +1054,10 @@
         <v>0.9923697257955202</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.02888722578051672</v>
+        <v>-0.02888722818772815</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1.060377895918552</v>
+        <v>1.060377901175519</v>
       </c>
     </row>
     <row r="18">
@@ -1079,10 +1079,10 @@
         <v>0.9535211430164198</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.1220363745826194</v>
+        <v>0.1220362134342508</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.7943028621578481</v>
+        <v>0.7943030903155814</v>
       </c>
     </row>
     <row r="19">
@@ -1104,10 +1104,10 @@
         <v>0.9878038066806144</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-0.06062918220140889</v>
+        <v>-0.06062873724857742</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1.133250374371495</v>
+        <v>1.1332493007963</v>
       </c>
     </row>
     <row r="20">
@@ -1129,10 +1129,10 @@
         <v>0.9295283057246148</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.03360076476281404</v>
+        <v>0.03360051231671157</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.9360398881234443</v>
+        <v>0.9360403453593833</v>
       </c>
     </row>
     <row r="21">
@@ -1179,10 +1179,10 @@
         <v>0.9887123252954994</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.001211391988220623</v>
+        <v>0.001211254634403636</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.9975816113352296</v>
+        <v>0.9975818850469979</v>
       </c>
     </row>
     <row r="23">
@@ -1204,10 +1204,10 @@
         <v>1.152111238395737</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-0.2497689417360024</v>
+        <v>-0.2497687016259206</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.776682896440897</v>
+        <v>1.776681759193202</v>
       </c>
     </row>
     <row r="24">
@@ -1229,10 +1229,10 @@
         <v>0.9604566236375061</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-0.2240498316814782</v>
+        <v>-0.2240500650023255</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1.660857364858337</v>
+        <v>1.660858363666864</v>
       </c>
     </row>
     <row r="25">
@@ -1254,10 +1254,10 @@
         <v>1.208353246583336</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-0.1831365983806144</v>
+        <v>-0.1831365610445778</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1.498653122436334</v>
+        <v>1.498652985439711</v>
       </c>
     </row>
     <row r="26">
@@ -1279,10 +1279,10 @@
         <v>0.857124786546162</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.0767789742180931</v>
+        <v>0.0767788355086978</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.8624756976669954</v>
+        <v>0.8624759198732391</v>
       </c>
     </row>
     <row r="27">
@@ -1304,10 +1304,10 @@
         <v>0.9387485503786788</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.07421923875024605</v>
+        <v>0.074219387625583</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.8665909469703643</v>
+        <v>0.8665907067698769</v>
       </c>
     </row>
     <row r="28">
@@ -1329,10 +1329,10 @@
         <v>0.9622415103954454</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.164008517914757</v>
+        <v>0.1640085904941517</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.7380532266449107</v>
+        <v>0.7380531346052895</v>
       </c>
     </row>
     <row r="29">
@@ -1354,10 +1354,10 @@
         <v>0.9236868300043514</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.008019690538680679</v>
+        <v>0.008019583403774622</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.9841515225572447</v>
+        <v>0.9841517317535505</v>
       </c>
     </row>
     <row r="30">
@@ -1379,10 +1379,10 @@
         <v>1.140325898830826</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-0.2507480697494133</v>
+        <v>-0.2507479901169969</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1.7813294954971</v>
+        <v>1.781329116848627</v>
       </c>
     </row>
     <row r="31">
@@ -1404,10 +1404,10 @@
         <v>0.8726609769291781</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.2123879532281372</v>
+        <v>0.2123876695250229</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.6803255402541909</v>
+        <v>0.6803258586515187</v>
       </c>
     </row>
     <row r="32">
@@ -1429,10 +1429,10 @@
         <v>0.971861873206222</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.02733945658285974</v>
+        <v>0.02733969698402072</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.9474843900035317</v>
+        <v>0.9474839465741161</v>
       </c>
     </row>
     <row r="33">
@@ -1454,10 +1454,10 @@
         <v>1.032451781203036</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-0.006188681909835902</v>
+        <v>-0.006188909686129951</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1.012493218660963</v>
+        <v>1.012493682777296</v>
       </c>
     </row>
     <row r="34">
@@ -1479,10 +1479,10 @@
         <v>0.9636033160989426</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.03916169743892106</v>
+        <v>0.03916182101195664</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.9260485129490527</v>
+        <v>0.9260482927049738</v>
       </c>
     </row>
     <row r="35">
@@ -1504,10 +1504,10 @@
         <v>0.9580497393985004</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.1548226289151955</v>
+        <v>0.1548227562674951</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.7498414248919626</v>
+        <v>0.7498412595089651</v>
       </c>
     </row>
     <row r="36">
@@ -1529,10 +1529,10 @@
         <v>0.9311717640044544</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.07899666343896872</v>
+        <v>0.07899685442700721</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.858934004705074</v>
+        <v>0.858933700633555</v>
       </c>
     </row>
     <row r="37">
@@ -1554,10 +1554,10 @@
         <v>0.9422614020637016</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.08563255734836273</v>
+        <v>0.08563236518577044</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.8484656837509729</v>
+        <v>0.8484659841167043</v>
       </c>
     </row>
     <row r="38">
@@ -1579,10 +1579,10 @@
         <v>1.000784713254058</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.004802606216045779</v>
+        <v>0.00480244317265166</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.9904635422030826</v>
+        <v>0.9904638636365183</v>
       </c>
     </row>
     <row r="39">
@@ -1604,10 +1604,10 @@
         <v>1.187452557550319</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.1429661147929286</v>
+        <v>0.1429661379912008</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.7654790155127723</v>
+        <v>0.7654789844396026</v>
       </c>
     </row>
     <row r="40">
@@ -1629,10 +1629,10 @@
         <v>1.301695888634536</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>-0.02395666979894417</v>
+        <v>-0.02395646024865339</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1.049691798362522</v>
+        <v>1.049691347638371</v>
       </c>
     </row>
     <row r="41">
@@ -1654,10 +1654,10 @@
         <v>0.7856559601127485</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.1088012994108971</v>
+        <v>0.1088012187721632</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.8133782359754479</v>
+        <v>0.8133783542830263</v>
       </c>
     </row>
     <row r="42">
@@ -1729,10 +1729,10 @@
         <v>0.8960977549701413</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.1176068331579609</v>
+        <v>0.1176066314065773</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.800611645827335</v>
+        <v>0.8006119348816719</v>
       </c>
     </row>
     <row r="45">
@@ -1754,10 +1754,10 @@
         <v>0.870377843369757</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.2599919668202599</v>
+        <v>0.2599924650565644</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.6298896140091308</v>
+        <v>0.6298891158572447</v>
       </c>
     </row>
     <row r="46">
@@ -1779,10 +1779,10 @@
         <v>1.080556042343192</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.01196646244274691</v>
+        <v>0.01196638823535223</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.9764899106495937</v>
+        <v>0.9764900538614151</v>
       </c>
     </row>
     <row r="47">
@@ -1804,10 +1804,10 @@
         <v>1.055384676976521</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>-0.07364829087902502</v>
+        <v>-0.07364849281799779</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>1.165328011080739</v>
+        <v>1.165328519149577</v>
       </c>
     </row>
     <row r="48">
@@ -1829,10 +1829,10 @@
         <v>0.8124073373168651</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.0692118079226125</v>
+        <v>0.06921181321154357</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.8747269505482094</v>
+        <v>0.8747269418944131</v>
       </c>
     </row>
     <row r="49">
@@ -1854,10 +1854,10 @@
         <v>0.9273208253828208</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>-0.0255675434609216</v>
+        <v>-0.02556740234817645</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>1.053165242878092</v>
+        <v>1.053164937849241</v>
       </c>
     </row>
     <row r="50">
@@ -1879,10 +1879,10 @@
         <v>1.020502470298805</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>-0.004998114292780631</v>
+        <v>-0.004998333962024648</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>1.010071674598626</v>
+        <v>1.010072120591258</v>
       </c>
     </row>
     <row r="51">
@@ -1904,10 +1904,10 @@
         <v>0.947050922347443</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.05579398255800871</v>
+        <v>0.05579428563846589</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.8971016080208348</v>
+        <v>0.8971010929698818</v>
       </c>
     </row>
     <row r="52">
@@ -1929,10 +1929,10 @@
         <v>0.9178444163991597</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>-0.02636931436640821</v>
+        <v>-0.02636938050255189</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>1.054900490004927</v>
+        <v>1.054900633318112</v>
       </c>
     </row>
     <row r="53">
@@ -1954,10 +1954,10 @@
         <v>0.9012367883774663</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.1244544633344791</v>
+        <v>0.1244543109915703</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.7908903102134078</v>
+        <v>0.7908905245156472</v>
       </c>
     </row>
     <row r="54">
@@ -1979,10 +1979,10 @@
         <v>0.9861767286709302</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.08228116793085949</v>
+        <v>0.08228123695056544</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.8537285334541932</v>
+        <v>0.853728424565508</v>
       </c>
     </row>
     <row r="55">
@@ -2004,10 +2004,10 @@
         <v>0.9548946305726876</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.2316222249405868</v>
+        <v>0.2316221070924096</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.6592421475690794</v>
+        <v>0.6592422737287004</v>
       </c>
     </row>
     <row r="56">
@@ -2029,10 +2029,10 @@
         <v>0.9541320909722018</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>-0.02517184367352054</v>
+        <v>-0.02517184608209688</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>1.052310420046947</v>
+        <v>1.052310425246981</v>
       </c>
     </row>
     <row r="57">
@@ -2054,10 +2054,10 @@
         <v>0.9418538915966996</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.1482101137295451</v>
+        <v>0.1482099319650567</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.758502932442185</v>
+        <v>0.7585031725880059</v>
       </c>
     </row>
     <row r="58">
@@ -2079,10 +2079,10 @@
         <v>1.099935334897597</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>-0.07455908150910806</v>
+        <v>-0.07455884417181569</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>1.167622900135464</v>
+        <v>1.1676223012418</v>
       </c>
     </row>
     <row r="59">
@@ -2104,10 +2104,10 @@
         <v>0.8733386651821466</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.2341669114563416</v>
+        <v>0.234167096203266</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.6565264125555101</v>
+        <v>0.656526215999911</v>
       </c>
     </row>
     <row r="60">
@@ -2129,10 +2129,10 @@
         <v>1.01400288589504</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.2780535217596904</v>
+        <v>0.2780534801368559</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.6122121116958058</v>
+        <v>0.6122121515720774</v>
       </c>
     </row>
     <row r="61">
@@ -2154,10 +2154,10 @@
         <v>0.9160517804201327</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>-0.09981002120570948</v>
+        <v>-0.09981018520470619</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1.234046862392376</v>
+        <v>1.234047312036356</v>
       </c>
     </row>
     <row r="62">
@@ -2179,10 +2179,10 @@
         <v>1.112119386768055</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>-0.1674542287481032</v>
+        <v>-0.1674542396420752</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>1.442725677897541</v>
+        <v>1.442725715654056</v>
       </c>
     </row>
     <row r="63">
@@ -2204,10 +2204,10 @@
         <v>1.062685451631391</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>-0.004124935826256948</v>
+        <v>-0.004124858007035659</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>1.008301199138703</v>
+        <v>1.008301041558284</v>
       </c>
     </row>
     <row r="64">
@@ -2229,10 +2229,10 @@
         <v>0.9296802682757126</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.1191571079042555</v>
+        <v>0.1191570294390476</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.7983951413451159</v>
+        <v>0.7983952532976683</v>
       </c>
     </row>
     <row r="65">
@@ -2254,10 +2254,10 @@
         <v>1.200190656587331</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>-0.3202740638430636</v>
+        <v>-0.3202740161868048</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>2.164374043469827</v>
+        <v>2.164373739977043</v>
       </c>
     </row>
     <row r="66">
@@ -2279,10 +2279,10 @@
         <v>0.9963421662408478</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.006739763459490788</v>
+        <v>0.006739454021604363</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.98665553195043</v>
+        <v>0.9866561384800502</v>
       </c>
     </row>
     <row r="67">
@@ -2304,10 +2304,10 @@
         <v>1.18803474289766</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>-0.1879710965016489</v>
+        <v>-0.1879708981389784</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>1.516551015734257</v>
+        <v>1.51655027480743</v>
       </c>
     </row>
     <row r="68">
@@ -2329,10 +2329,10 @@
         <v>0.8382858229126688</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.1981657344436987</v>
+        <v>0.198166188547769</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.6965723145912263</v>
+        <v>0.6965717865905758</v>
       </c>
     </row>
     <row r="69">
@@ -2354,10 +2354,10 @@
         <v>1.086837917632202</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>-0.1689697446694109</v>
+        <v>-0.168969954550624</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>1.447992555757407</v>
+        <v>1.447993287154483</v>
       </c>
     </row>
     <row r="70">
@@ -2379,10 +2379,10 @@
         <v>1.213175071407492</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>-0.1955340764311234</v>
+        <v>-0.195534254115783</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>1.545199983994844</v>
+        <v>1.545200666580435</v>
       </c>
     </row>
     <row r="71">
@@ -2404,10 +2404,10 @@
         <v>0.855814644350068</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.1118706750789171</v>
+        <v>0.1118707714577905</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.8088936902866886</v>
+        <v>0.8088935500540984</v>
       </c>
     </row>
     <row r="72">
@@ -2429,10 +2429,10 @@
         <v>0.8969474204044003</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.2541551382415801</v>
+        <v>0.2541552270776135</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.6357662602453675</v>
+        <v>0.6357661701784452</v>
       </c>
     </row>
     <row r="73">
@@ -2479,10 +2479,10 @@
         <v>0.8852560567072887</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.3368689099972106</v>
+        <v>0.3368690408023851</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.559528680898372</v>
+        <v>0.5595285714048601</v>
       </c>
     </row>
     <row r="75">
@@ -2504,10 +2504,10 @@
         <v>1.050645569002066</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.1883093324211624</v>
+        <v>0.1883092161517261</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.708175640858745</v>
+        <v>0.7081757794408335</v>
       </c>
     </row>
     <row r="76">
@@ -2529,10 +2529,10 @@
         <v>0.9304259309730823</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.1966626279293711</v>
+        <v>0.1966625455901805</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.698323317643132</v>
+        <v>0.6983234137427031</v>
       </c>
     </row>
     <row r="77">
@@ -2554,10 +2554,10 @@
         <v>0.9694982234937056</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>-0.001008165368845293</v>
+        <v>-0.001008027823494517</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>1.002019384033882</v>
+        <v>1.002019108109546</v>
       </c>
     </row>
     <row r="78">
@@ -2579,10 +2579,10 @@
         <v>0.9913625810824932</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.3634365332711422</v>
+        <v>0.3634364393620109</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.5379354267805821</v>
+        <v>0.5379355008831204</v>
       </c>
     </row>
     <row r="79">
@@ -2654,10 +2654,10 @@
         <v>1.032619118725376</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.05619664404476143</v>
+        <v>0.05619656225124547</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.8964177213365556</v>
+        <v>0.8964178601765456</v>
       </c>
     </row>
     <row r="82">
@@ -2679,10 +2679,10 @@
         <v>1.10263682294205</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>-0.1185781295896224</v>
+        <v>-0.1185779838893664</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>1.287159467406958</v>
+        <v>1.287159041868577</v>
       </c>
     </row>
     <row r="83">
@@ -2704,10 +2704,10 @@
         <v>1.043418468810109</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>-0.06250724843451383</v>
+        <v>-0.06250724294263921</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>1.137795371811613</v>
+        <v>1.1377953584811</v>
       </c>
     </row>
     <row r="84">
@@ -2729,10 +2729,10 @@
         <v>0.8396361081156987</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.1468858727358351</v>
+        <v>0.1468857652521582</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.7602555402384349</v>
+        <v>0.7602556827374825</v>
       </c>
     </row>
     <row r="85">
@@ -2779,10 +2779,10 @@
         <v>0.9672203593217011</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.242417620068432</v>
+        <v>0.2424175429011504</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.6478355795622104</v>
+        <v>0.6478356600371078</v>
       </c>
     </row>
     <row r="87">
@@ -2804,10 +2804,10 @@
         <v>0.9011908328520706</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.2858095456014653</v>
+        <v>0.2858097496850216</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.6048486405751153</v>
+        <v>0.6048484485721355</v>
       </c>
     </row>
     <row r="88">
@@ -2829,10 +2829,10 @@
         <v>0.9386281887403397</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.1421811675620739</v>
+        <v>0.1421810572167577</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.7665315054625226</v>
+        <v>0.7665316535706792</v>
       </c>
     </row>
     <row r="89">
@@ -2879,10 +2879,10 @@
         <v>0.9077465777794721</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.2688710508743717</v>
+        <v>0.2688711393283107</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.6211049947765067</v>
+        <v>0.6211049081811389</v>
       </c>
     </row>
     <row r="91">
@@ -2904,10 +2904,10 @@
         <v>0.9319221176611617</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.1269431868627044</v>
+        <v>0.1269431083026671</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.7874009880243269</v>
+        <v>0.7874010978049409</v>
       </c>
     </row>
     <row r="92">
@@ -2954,10 +2954,10 @@
         <v>0.9531969858300583</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.02008214562373478</v>
+        <v>0.02008208031891745</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.9610139846261756</v>
+        <v>0.9610141076728321</v>
       </c>
     </row>
     <row r="94">
@@ -2979,10 +2979,10 @@
         <v>0.9586163156807694</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.01742800403576883</v>
+        <v>0.01742806917067452</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.9660344757217331</v>
+        <v>0.9660343520322766</v>
       </c>
     </row>
     <row r="95">
@@ -3054,10 +3054,10 @@
         <v>1.049436799471192</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>-0.02857691784311611</v>
+        <v>-0.02857680729967016</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>1.059700557425121</v>
+        <v>1.059700316247135</v>
       </c>
     </row>
     <row r="98">
@@ -3079,10 +3079,10 @@
         <v>0.9465483128657197</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>-0.1058901733604136</v>
+        <v>-0.1058902751059577</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>1.25088753270327</v>
+        <v>1.250887817393697</v>
       </c>
     </row>
     <row r="99">
@@ -3104,10 +3104,10 @@
         <v>1.026615030088406</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.04039309306242167</v>
+        <v>0.04039315669854515</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.9238576924744808</v>
+        <v>0.9238575794581273</v>
       </c>
     </row>
     <row r="100">
@@ -3129,10 +3129,10 @@
         <v>1.122982133980397</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>-0.1323249309931265</v>
+        <v>-0.1323249840648691</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>1.328268159144804</v>
+        <v>1.328268321633079</v>
       </c>
     </row>
     <row r="101">
@@ -3179,10 +3179,10 @@
         <v>0.8850712241425256</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>0.240635387014742</v>
+        <v>0.2406355273027898</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0.6496982110985062</v>
+        <v>0.6496980641659276</v>
       </c>
     </row>
     <row r="103">
@@ -3204,10 +3204,10 @@
         <v>0.9055585326855982</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0.1692516955417807</v>
+        <v>0.1692514502480753</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.7314488868007236</v>
+        <v>0.7314491936976302</v>
       </c>
     </row>
     <row r="104">
@@ -3229,10 +3229,10 @@
         <v>0.9565816763960454</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>0.1258306729394936</v>
+        <v>0.1258308785272324</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.7889579315325774</v>
+        <v>0.7889576433897214</v>
       </c>
     </row>
     <row r="105">
@@ -3254,10 +3254,10 @@
         <v>0.9606567708776664</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>-0.02074547328268472</v>
+        <v>-0.02074564330151807</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>1.042818733593172</v>
+        <v>1.042819095703055</v>
       </c>
     </row>
     <row r="106">
@@ -3279,10 +3279,10 @@
         <v>0.930810829949856</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.07125111963927333</v>
+        <v>0.07125121360969189</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.8713997325660584</v>
+        <v>0.8713995796872697</v>
       </c>
     </row>
     <row r="107">
@@ -3510,8 +3510,33 @@
         <v>1.110909201347264</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="n">
+        <v>0.0339</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0.935498142142787</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>-0.0006349317981017011</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>1.001271074036043</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>0.003298534030631073</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>0.9934354299520529</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G115"/>
+  <autoFilter ref="A1:G116"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/isolated_excel/MPPM Recalculation.xlsx
+++ b/isolated_excel/MPPM Recalculation.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPPM Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Inputs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MPPM Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Monthly Inputs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Source and Method" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MPPM Summary'!$A$1:$I$4</definedName>
@@ -510,7 +510,7 @@
         <v>35.16</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>46.57265489959188</v>
+        <v>46.57265489959113</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>115</v>
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.03263370241484337</v>
+        <v>0.03263370241484307</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>47.01293292530049</v>
+        <v>47.01293292530011</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>11.85293292530049</v>
+        <v>11.85293292530012</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>3</v>
@@ -554,13 +554,13 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.009824109332120121</v>
+        <v>0.009824109332120233</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>12.44724565179145</v>
+        <v>12.44724565179176</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>4.077245651791451</v>
+        <v>4.077245651791761</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>3</v>
@@ -576,7 +576,7 @@
         <v>21.19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27.82296044992847</v>
+        <v>27.82295882614039</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>115</v>
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.0198279274293732</v>
+        <v>0.01982792636944819</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>26.56767680106729</v>
+        <v>26.56767522253958</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5.377676801067285</v>
+        <v>5.377675222539576</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3</v>
@@ -679,10 +679,10 @@
         <v>0.9631201026442409</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.02285892531040834</v>
+        <v>0.02285938558352174</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.95580329155417</v>
+        <v>0.9558024313568368</v>
       </c>
     </row>
     <row r="3">
@@ -704,10 +704,10 @@
         <v>0.9250752875147531</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-0.06935284474603898</v>
+        <v>-0.06935283243179036</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.15459558285616</v>
+        <v>1.154595552301128</v>
       </c>
     </row>
     <row r="4">
@@ -729,10 +729,10 @@
         <v>0.9976745395509637</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.07341355091686697</v>
+        <v>0.0734134415145471</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.8678923350732001</v>
+        <v>0.8678925119844181</v>
       </c>
     </row>
     <row r="5">
@@ -754,10 +754,10 @@
         <v>0.9797710949826629</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-0.04250421583286856</v>
+        <v>-0.04250421205546351</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.090752605553657</v>
+        <v>1.090752596947427</v>
       </c>
     </row>
     <row r="6">
@@ -779,10 +779,10 @@
         <v>0.9724380915636373</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.3854462770320806</v>
+        <v>0.3854462412563477</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.5209794825836636</v>
+        <v>0.5209795094896849</v>
       </c>
     </row>
     <row r="7">
@@ -804,10 +804,10 @@
         <v>0.9876324120800218</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.001454972753595296</v>
+        <v>0.001454503699099385</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9970963930319254</v>
+        <v>0.9970973270586911</v>
       </c>
     </row>
     <row r="8">
@@ -829,10 +829,10 @@
         <v>0.9601089735562846</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.1241693290371488</v>
+        <v>0.1241699140486252</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.7912915639146314</v>
+        <v>0.7912907403478026</v>
       </c>
     </row>
     <row r="9">
@@ -854,10 +854,10 @@
         <v>0.9939038411792369</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.04356141099001598</v>
+        <v>0.04356164383561634</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9182564284428408</v>
+        <v>0.9182560186693564</v>
       </c>
     </row>
     <row r="10">
@@ -879,10 +879,10 @@
         <v>0.9599867759537827</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.05506394330039477</v>
+        <v>0.05506392446076891</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8983435156379461</v>
+        <v>0.8983435477202788</v>
       </c>
     </row>
     <row r="11">
@@ -904,10 +904,10 @@
         <v>0.9549146468467293</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1568495448071063</v>
+        <v>0.1568497101328961</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.7472161327279129</v>
+        <v>0.7472159191580994</v>
       </c>
     </row>
     <row r="12">
@@ -929,10 +929,10 @@
         <v>0.9413715807084023</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-0.02882116699895132</v>
+        <v>-0.02882171416760748</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1.060233648768297</v>
+        <v>1.060234843454777</v>
       </c>
     </row>
     <row r="13">
@@ -954,10 +954,10 @@
         <v>0.9781287914115532</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0.03592226844671587</v>
+        <v>-0.03592256053872533</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1.075909883095237</v>
+        <v>1.075910535044374</v>
       </c>
     </row>
     <row r="14">
@@ -979,10 +979,10 @@
         <v>0.8946259836989391</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.270283864222761</v>
+        <v>0.2702841717105691</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.6197241735757516</v>
+        <v>0.619723873552168</v>
       </c>
     </row>
     <row r="15">
@@ -1004,10 +1004,10 @@
         <v>1.077996580636878</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-0.01484787048851988</v>
+        <v>-0.01484755857082565</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1.03037045957078</v>
+        <v>1.030369807101754</v>
       </c>
     </row>
     <row r="16">
@@ -1029,10 +1029,10 @@
         <v>1.05283346576593</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.04301649959727905</v>
+        <v>-0.0430167319765653</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.09192070178464</v>
+        <v>1.091921232075592</v>
       </c>
     </row>
     <row r="17">
@@ -1054,10 +1054,10 @@
         <v>0.9923697257955202</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.02888722818772815</v>
+        <v>-0.02888723059494003</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1.060377901175519</v>
+        <v>1.060377906432487</v>
       </c>
     </row>
     <row r="18">
@@ -1079,10 +1079,10 @@
         <v>0.9535211430164198</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.1220362134342508</v>
+        <v>0.1220363097163717</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.7943030903155814</v>
+        <v>0.7943029539970288</v>
       </c>
     </row>
     <row r="19">
@@ -1179,10 +1179,10 @@
         <v>0.9887123252954994</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.001211254634403636</v>
+        <v>0.001211391988220623</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.9975818850469979</v>
+        <v>0.9975816113352296</v>
       </c>
     </row>
     <row r="23">
@@ -1204,10 +1204,10 @@
         <v>1.152111238395737</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-0.2497687016259206</v>
+        <v>-0.2497688045483735</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.776681759193202</v>
+        <v>1.776682246670818</v>
       </c>
     </row>
     <row r="24">
@@ -1254,10 +1254,10 @@
         <v>1.208353246583336</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-0.1831365610445778</v>
+        <v>-0.1831363842994731</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1.498652985439711</v>
+        <v>1.498652336911499</v>
       </c>
     </row>
     <row r="26">
@@ -1279,10 +1279,10 @@
         <v>0.857124786546162</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.0767788355086978</v>
+        <v>0.07677881889603055</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.8624759198732391</v>
+        <v>0.8624759464859943</v>
       </c>
     </row>
     <row r="27">
@@ -1304,10 +1304,10 @@
         <v>0.9387485503786788</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.074219387625583</v>
+        <v>0.07421897082719897</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.8665907067698769</v>
+        <v>0.8665913792466923</v>
       </c>
     </row>
     <row r="28">
@@ -1329,10 +1329,10 @@
         <v>0.9622415103954454</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.1640085904941517</v>
+        <v>0.1640088082323901</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.7380531346052895</v>
+        <v>0.738052858486461</v>
       </c>
     </row>
     <row r="29">
@@ -1354,10 +1354,10 @@
         <v>0.9236868300043514</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.008019583403774622</v>
+        <v>0.008019797673586959</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.9841517317535505</v>
+        <v>0.9841513133610053</v>
       </c>
     </row>
     <row r="30">
@@ -1379,10 +1379,10 @@
         <v>1.140325898830826</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-0.2507479901169969</v>
+        <v>-0.2507481493818129</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1.781329116848627</v>
+        <v>1.781329874145614</v>
       </c>
     </row>
     <row r="31">
@@ -1404,10 +1404,10 @@
         <v>0.8726609769291781</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.2123876695250229</v>
+        <v>0.2123879532281372</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.6803258586515187</v>
+        <v>0.6803255402541909</v>
       </c>
     </row>
     <row r="32">
@@ -1429,10 +1429,10 @@
         <v>0.971861873206222</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.02733969698402072</v>
+        <v>0.02733922257928567</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.9474839465741161</v>
+        <v>0.947484821632645</v>
       </c>
     </row>
     <row r="33">
@@ -1454,10 +1454,10 @@
         <v>1.032451781203036</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-0.006188909686129951</v>
+        <v>-0.006188911095817207</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1.012493682777296</v>
+        <v>1.012493685649672</v>
       </c>
     </row>
     <row r="34">
@@ -1479,10 +1479,10 @@
         <v>0.9636033160989426</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.03916182101195664</v>
+        <v>0.0391620591824553</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.9260482927049738</v>
+        <v>0.9260478682141902</v>
       </c>
     </row>
     <row r="35">
@@ -1504,10 +1504,10 @@
         <v>0.9580497393985004</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.1548227562674951</v>
+        <v>0.1548229768248279</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.7498412595089651</v>
+        <v>0.7498409730876247</v>
       </c>
     </row>
     <row r="36">
@@ -1529,10 +1529,10 @@
         <v>0.9311717640044544</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.07899685442700721</v>
+        <v>0.07899645736355199</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.858933700633555</v>
+        <v>0.8589343327973464</v>
       </c>
     </row>
     <row r="37">
@@ -1554,10 +1554,10 @@
         <v>0.9422614020637016</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.08563236518577044</v>
+        <v>0.08563282285618801</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.8484659841167043</v>
+        <v>0.8484652687409506</v>
       </c>
     </row>
     <row r="38">
@@ -1579,10 +1579,10 @@
         <v>1.000784713254058</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.00480244317265166</v>
+        <v>0.004802197433110722</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.9904638636365183</v>
+        <v>0.9904643481023476</v>
       </c>
     </row>
     <row r="39">
@@ -1604,10 +1604,10 @@
         <v>1.187452557550319</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.1429661379912008</v>
+        <v>0.1429664625194604</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.7654789844396026</v>
+        <v>0.7654785497470101</v>
       </c>
     </row>
     <row r="40">
@@ -1629,10 +1629,10 @@
         <v>1.301695888634536</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>-0.02395646024865339</v>
+        <v>-0.02395680836540848</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1.049691347638371</v>
+        <v>1.049692096406897</v>
       </c>
     </row>
     <row r="41">
@@ -1654,10 +1654,10 @@
         <v>0.7856559601127485</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.1088012187721632</v>
+        <v>0.1088013721369481</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.8133783542830263</v>
+        <v>0.8133781292768334</v>
       </c>
     </row>
     <row r="42">
@@ -1679,10 +1679,10 @@
         <v>0.9111424311350199</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.2146570368602847</v>
+        <v>0.2146568260115995</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.6777861013763365</v>
+        <v>0.6777863366861255</v>
       </c>
     </row>
     <row r="43">
@@ -1704,10 +1704,10 @@
         <v>0.9613795399637081</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.07059713934785017</v>
+        <v>0.07059747096386237</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.8724646565916658</v>
+        <v>0.8724641161024282</v>
       </c>
     </row>
     <row r="44">
@@ -1729,10 +1729,10 @@
         <v>0.8960977549701413</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.1176066314065773</v>
+        <v>0.1176066076792814</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.8006119348816719</v>
+        <v>0.8006119688763823</v>
       </c>
     </row>
     <row r="45">
@@ -1754,10 +1754,10 @@
         <v>0.870377843369757</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.2599924650565644</v>
+        <v>0.2599917862993668</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.6298891158572447</v>
+        <v>0.6298897944995833</v>
       </c>
     </row>
     <row r="46">
@@ -1779,10 +1779,10 @@
         <v>1.080556042343192</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.01196638823535223</v>
+        <v>0.01196682233590973</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.9764900538614151</v>
+        <v>0.9764892160972187</v>
       </c>
     </row>
     <row r="47">
@@ -1804,10 +1804,10 @@
         <v>1.055384676976521</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>-0.07364849281799779</v>
+        <v>-0.07364827523864081</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>1.165328519149577</v>
+        <v>1.165327971730291</v>
       </c>
     </row>
     <row r="48">
@@ -1829,10 +1829,10 @@
         <v>0.8124073373168651</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.06921181321154357</v>
+        <v>0.06921163922267226</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.8747269418944131</v>
+        <v>0.8747272265766223</v>
       </c>
     </row>
     <row r="49">
@@ -1854,10 +1854,10 @@
         <v>0.9273208253828208</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>-0.02556740234817645</v>
+        <v>-0.02556768457364667</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>1.053164937849241</v>
+        <v>1.053165547907032</v>
       </c>
     </row>
     <row r="50">
@@ -1879,10 +1879,10 @@
         <v>1.020502470298805</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>-0.004998333962024648</v>
+        <v>-0.004998041314080548</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>1.010072120591258</v>
+        <v>1.010071526430646</v>
       </c>
     </row>
     <row r="51">
@@ -1904,10 +1904,10 @@
         <v>0.947050922347443</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.05579428563846589</v>
+        <v>0.05579405627172118</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.8971010929698818</v>
+        <v>0.897101482752678</v>
       </c>
     </row>
     <row r="52">
@@ -1929,10 +1929,10 @@
         <v>0.9178444163991597</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>-0.02636938050255189</v>
+        <v>-0.0263693823436163</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>1.054900633318112</v>
+        <v>1.054900637307592</v>
       </c>
     </row>
     <row r="53">
@@ -1954,10 +1954,10 @@
         <v>0.9012367883774663</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.1244543109915703</v>
+        <v>0.1244544633344791</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.7908905245156472</v>
+        <v>0.7908903102134078</v>
       </c>
     </row>
     <row r="54">
@@ -1979,10 +1979,10 @@
         <v>0.9861767286709302</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.08228123695056544</v>
+        <v>0.0822810403859966</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.853728424565508</v>
+        <v>0.8537287346749318</v>
       </c>
     </row>
     <row r="55">
@@ -2004,10 +2004,10 @@
         <v>0.9548946305726876</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.2316221070924096</v>
+        <v>0.2316224879332291</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.6592422737287004</v>
+        <v>0.6592418660285626</v>
       </c>
     </row>
     <row r="56">
@@ -2029,10 +2029,10 @@
         <v>0.9541320909722018</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>-0.02517184608209688</v>
+        <v>-0.02517193695026387</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>1.052310425246981</v>
+        <v>1.052310621428292</v>
       </c>
     </row>
     <row r="57">
@@ -2054,10 +2054,10 @@
         <v>0.9418538915966996</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.1482099319650567</v>
+        <v>0.1482098192612498</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.7585031725880059</v>
+        <v>0.7585033214914518</v>
       </c>
     </row>
     <row r="58">
@@ -2079,10 +2079,10 @@
         <v>1.099935334897597</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>-0.07455884417181569</v>
+        <v>-0.07455892965801925</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>1.1676223012418</v>
+        <v>1.167622516956459</v>
       </c>
     </row>
     <row r="59">
@@ -2104,10 +2104,10 @@
         <v>0.8733386651821466</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.234167096203266</v>
+        <v>0.2341668407136812</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.656526215999911</v>
+        <v>0.6565264878199312</v>
       </c>
     </row>
     <row r="60">
@@ -2129,10 +2129,10 @@
         <v>1.01400288589504</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.2780534801368559</v>
+        <v>0.2780537130761895</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.6122121515720774</v>
+        <v>0.6122119284073134</v>
       </c>
     </row>
     <row r="61">
@@ -2154,10 +2154,10 @@
         <v>0.9160517804201327</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>-0.09981018520470619</v>
+        <v>-0.0998100797688396</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1.234047312036356</v>
+        <v>1.234047022957714</v>
       </c>
     </row>
     <row r="62">
@@ -2179,10 +2179,10 @@
         <v>1.112119386768055</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>-0.1674542396420752</v>
+        <v>-0.167454434811324</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>1.442725715654056</v>
+        <v>1.442726392075237</v>
       </c>
     </row>
     <row r="63">
@@ -2204,10 +2204,10 @@
         <v>1.062685451631391</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>-0.004124858007035659</v>
+        <v>-0.004124624549298961</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>1.008301041558284</v>
+        <v>1.008300568817101</v>
       </c>
     </row>
     <row r="64">
@@ -2229,10 +2229,10 @@
         <v>0.9296802682757126</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.1191570294390476</v>
+        <v>0.1191571079042555</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.7983952532976683</v>
+        <v>0.7983951413451159</v>
       </c>
     </row>
     <row r="65">
@@ -2254,10 +2254,10 @@
         <v>1.200190656587331</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>-0.3202740161868048</v>
+        <v>-0.3202741339540492</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>2.164373739977043</v>
+        <v>2.164374489962782</v>
       </c>
     </row>
     <row r="66">
@@ -2279,10 +2279,10 @@
         <v>0.9963421662408478</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.006739454021604363</v>
+        <v>0.006739661008697384</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.9866561384800502</v>
+        <v>0.986655732764307</v>
       </c>
     </row>
     <row r="67">
@@ -2304,10 +2304,10 @@
         <v>1.18803474289766</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>-0.1879708981389784</v>
+        <v>-0.1879709813357917</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>1.51655027480743</v>
+        <v>1.516550585565183</v>
       </c>
     </row>
     <row r="68">
@@ -2329,10 +2329,10 @@
         <v>0.8382858229126688</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.198166188547769</v>
+        <v>0.19816581003128</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.6965717865905758</v>
+        <v>0.6965722267031987</v>
       </c>
     </row>
     <row r="69">
@@ -2354,10 +2354,10 @@
         <v>1.086837917632202</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>-0.168969954550624</v>
+        <v>-0.1689697973216241</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>1.447993287154483</v>
+        <v>1.447992739240546</v>
       </c>
     </row>
     <row r="70">
@@ -2379,10 +2379,10 @@
         <v>1.213175071407492</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>-0.195534254115783</v>
+        <v>-0.1955340888197248</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>1.545200666580435</v>
+        <v>1.545200031586336</v>
       </c>
     </row>
     <row r="71">
@@ -2404,10 +2404,10 @@
         <v>0.855814644350068</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.1118707714577905</v>
+        <v>0.1118708414046692</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.8088935500540984</v>
+        <v>0.8088934482804477</v>
       </c>
     </row>
     <row r="72">
@@ -2429,10 +2429,10 @@
         <v>0.8969474204044003</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.2541552270776135</v>
+        <v>0.2541550494055593</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.6357661701784452</v>
+        <v>0.6357663503122962</v>
       </c>
     </row>
     <row r="73">
@@ -2454,10 +2454,10 @@
         <v>1.126011828926274</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>-0.13644167486741</v>
+        <v>-0.1364415619095126</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>1.340962550409599</v>
+        <v>1.340962199599987</v>
       </c>
     </row>
     <row r="74">
@@ -2479,10 +2479,10 @@
         <v>0.8852560567072887</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.3368690408023851</v>
+        <v>0.3368687351278623</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.5595285714048601</v>
+        <v>0.5595288272768753</v>
       </c>
     </row>
     <row r="75">
@@ -2504,10 +2504,10 @@
         <v>1.050645569002066</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.1883092161517261</v>
+        <v>0.1883094302655908</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.7081757794408335</v>
+        <v>0.7081755242375415</v>
       </c>
     </row>
     <row r="76">
@@ -2529,10 +2529,10 @@
         <v>0.9304259309730823</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.1966625455901805</v>
+        <v>0.1966622823795958</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.6983234137427031</v>
+        <v>0.6983237209407104</v>
       </c>
     </row>
     <row r="77">
@@ -2554,10 +2554,10 @@
         <v>0.9694982234937056</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>-0.001008027823494517</v>
+        <v>-0.00100795915484464</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>1.002019108109546</v>
+        <v>1.002018970356102</v>
       </c>
     </row>
     <row r="78">
@@ -2579,10 +2579,10 @@
         <v>0.9913625810824932</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.3634364393620109</v>
+        <v>0.3634365332711422</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.5379355008831204</v>
+        <v>0.5379354267805821</v>
       </c>
     </row>
     <row r="79">
@@ -2604,10 +2604,10 @@
         <v>0.8798812409728222</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.1182106092275659</v>
+        <v>0.1182105081934617</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.7997473012290435</v>
+        <v>0.7997474457488012</v>
       </c>
     </row>
     <row r="80">
@@ -2629,10 +2629,10 @@
         <v>0.9387194711195235</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.1046520694763253</v>
+        <v>0.1046523499921483</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.819500039767608</v>
+        <v>0.8194996235593793</v>
       </c>
     </row>
     <row r="81">
@@ -2654,10 +2654,10 @@
         <v>1.032619118725376</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.05619656225124547</v>
+        <v>0.05619638947121319</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.8964178601765456</v>
+        <v>0.8964181534612434</v>
       </c>
     </row>
     <row r="82">
@@ -2679,10 +2679,10 @@
         <v>1.10263682294205</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>-0.1185779838893664</v>
+        <v>-0.1185780613309324</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>1.287159041868577</v>
+        <v>1.287159268047691</v>
       </c>
     </row>
     <row r="83">
@@ -2704,10 +2704,10 @@
         <v>1.043418468810109</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>-0.06250724294263921</v>
+        <v>-0.06250716057470163</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>1.1377953584811</v>
+        <v>1.137795158548154</v>
       </c>
     </row>
     <row r="84">
@@ -2729,10 +2729,10 @@
         <v>0.8396361081156987</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.1468857652521582</v>
+        <v>0.1468858589700071</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.7602556827374825</v>
+        <v>0.7602555584888074</v>
       </c>
     </row>
     <row r="85">
@@ -2754,10 +2754,10 @@
         <v>0.9149756157506371</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.05893413316042428</v>
+        <v>0.05893412834461786</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.8917889879681051</v>
+        <v>0.8917889960794372</v>
       </c>
     </row>
     <row r="86">
@@ -2779,10 +2779,10 @@
         <v>0.9672203593217011</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.2424175429011504</v>
+        <v>0.2424175241944488</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.6478356600371078</v>
+        <v>0.6478356795456357</v>
       </c>
     </row>
     <row r="87">
@@ -2804,10 +2804,10 @@
         <v>0.9011908328520706</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.2858097496850216</v>
+        <v>0.2858094213803009</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.6048484485721355</v>
+        <v>0.6048487574431439</v>
       </c>
     </row>
     <row r="88">
@@ -2829,10 +2829,10 @@
         <v>0.9386281887403397</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.1421810572167577</v>
+        <v>0.1421812779074114</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.7665316535706792</v>
+        <v>0.7665313573543803</v>
       </c>
     </row>
     <row r="89">
@@ -2879,10 +2879,10 @@
         <v>0.9077465777794721</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.2688711393283107</v>
+        <v>0.2688709624204324</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.6211049081811389</v>
+        <v>0.6211050813718927</v>
       </c>
     </row>
     <row r="91">
@@ -2904,10 +2904,10 @@
         <v>0.9319221176611617</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.1269431083026671</v>
+        <v>0.1269433351334972</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.7874010978049409</v>
+        <v>0.7874007808292401</v>
       </c>
     </row>
     <row r="92">
@@ -2929,10 +2929,10 @@
         <v>0.9760924573374677</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>-0.05277653562964368</v>
+        <v>-0.05277659422323111</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>1.114538575489416</v>
+        <v>1.114538713376244</v>
       </c>
     </row>
     <row r="93">
@@ -2979,10 +2979,10 @@
         <v>0.9586163156807694</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.01742806917067452</v>
+        <v>0.01742813318985359</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.9660343520322766</v>
+        <v>0.9660342304615784</v>
       </c>
     </row>
     <row r="95">
@@ -3004,10 +3004,10 @@
         <v>1.018385718385046</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.09321467648585813</v>
+        <v>0.09321460769799583</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.836737229972644</v>
+        <v>0.8367373352719453</v>
       </c>
     </row>
     <row r="96">
@@ -3029,10 +3029,10 @@
         <v>0.8921825152855977</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.04135289746672743</v>
+        <v>0.04135301258146518</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.9221554567718803</v>
+        <v>0.9221552528954302</v>
       </c>
     </row>
     <row r="97">
@@ -3054,10 +3054,10 @@
         <v>1.049436799471192</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>-0.02857680729967016</v>
+        <v>-0.02857691468412549</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>1.059700316247135</v>
+        <v>1.059700550532997</v>
       </c>
     </row>
     <row r="98">
@@ -3104,10 +3104,10 @@
         <v>1.026615030088406</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.04039315669854515</v>
+        <v>0.04039309306242167</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.9238575794581273</v>
+        <v>0.9238576924744808</v>
       </c>
     </row>
     <row r="100">
@@ -3129,10 +3129,10 @@
         <v>1.122982133980397</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>-0.1323249840648691</v>
+        <v>-0.1323249309931265</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>1.328268321633079</v>
+        <v>1.328268159144804</v>
       </c>
     </row>
     <row r="101">
@@ -3204,10 +3204,10 @@
         <v>0.9055585326855982</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0.1692514502480753</v>
+        <v>0.1692515633256428</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.7314491936976302</v>
+        <v>0.7314490522216738</v>
       </c>
     </row>
     <row r="104">
@@ -3229,10 +3229,10 @@
         <v>0.9565816763960454</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>0.1258308785272324</v>
+        <v>0.1258306729394936</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.7889576433897214</v>
+        <v>0.7889579315325774</v>
       </c>
     </row>
     <row r="105">
@@ -3254,10 +3254,10 @@
         <v>0.9606567708776664</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>-0.02074564330151807</v>
+        <v>-0.02074555918313137</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>1.042819095703055</v>
+        <v>1.042818916545825</v>
       </c>
     </row>
     <row r="106">
@@ -3354,10 +3354,10 @@
         <v>0.9987769482420827</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>0.05373093153479269</v>
+        <v>0.05373101785259271</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>0.9006178342221252</v>
+        <v>0.9006176866714778</v>
       </c>
     </row>
     <row r="110">
@@ -3379,10 +3379,10 @@
         <v>0.9716183111985258</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0.02482581715253174</v>
+        <v>0.02482573320254033</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0.952137970849248</v>
+        <v>0.9521381268406037</v>
       </c>
     </row>
     <row r="111">
